--- a/data/trans_orig/IP22B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22B-Estudios-trans_orig.xlsx
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,53%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19127</t>
+          <t>19432</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33512</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48097</t>
+          <t>48706</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39101</t>
+          <t>40151</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55512</t>
+          <t>56139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77891</t>
+          <t>79082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101125</t>
+          <t>101015</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,17%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34823</t>
+          <t>34232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49430</t>
+          <t>49031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45817</t>
+          <t>44817</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62048</t>
+          <t>60824</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83501</t>
+          <t>81855</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>104879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>55,21%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14593</t>
+          <t>14738</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15043</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26204</t>
+          <t>26037</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13315</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22607</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19177</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>28639</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35525</t>
+          <t>35292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>48938</t>
+          <t>47947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>66,81%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>12067</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>18872</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47412</t>
+          <t>47922</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65475</t>
+          <t>65970</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53575</t>
+          <t>53109</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72860</t>
+          <t>72309</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>105949</t>
+          <t>106784</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>132699</t>
+          <t>133466</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57131</t>
+          <t>57208</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>75453</t>
+          <t>75438</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>75664</t>
+          <t>76035</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94785</t>
+          <t>96142</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>140023</t>
+          <t>138737</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>166567</t>
+          <t>164741</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,32%</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17530</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28997</t>
+          <t>29221</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14328</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17275</t>
+          <t>17182</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>17685</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29173</t>
+          <t>28722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>60,76%</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36721</t>
+          <t>36493</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53462</t>
+          <t>52903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54039</t>
+          <t>53707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73732</t>
+          <t>73177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96137</t>
+          <t>95305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121304</t>
+          <t>120338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>49,88%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46413</t>
+          <t>47814</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63490</t>
+          <t>64367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59131</t>
+          <t>59747</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79335</t>
+          <t>79126</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112481</t>
+          <t>112014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138065</t>
+          <t>138626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,46%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>842</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7896</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>18596</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>18699</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33241</t>
+          <t>32669</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18961</t>
+          <t>19476</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30175</t>
+          <t>29928</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>20016</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30483</t>
+          <t>30887</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43047</t>
+          <t>43085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58009</t>
+          <t>57866</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57427</t>
+          <t>57040</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77891</t>
+          <t>77787</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77679</t>
+          <t>78319</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101451</t>
+          <t>102156</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>140872</t>
+          <t>140726</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>172315</t>
+          <t>172175</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>80017</t>
+          <t>80552</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>100950</t>
+          <t>101193</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>95974</t>
+          <t>96282</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>120723</t>
+          <t>120253</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>181853</t>
+          <t>183464</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>215366</t>
+          <t>216016</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,11%</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2318</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,31%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>76,26%</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22773</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36550</t>
+          <t>35896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18415</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32587</t>
+          <t>32828</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45295</t>
+          <t>45111</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64256</t>
+          <t>64520</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39882</t>
+          <t>40361</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53574</t>
+          <t>53796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48313</t>
+          <t>47514</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62289</t>
+          <t>61736</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92717</t>
+          <t>92079</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111993</t>
+          <t>112254</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,99%</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>14486</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>20542</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>21156</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13487</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22369</t>
+          <t>22558</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28718</t>
+          <t>27936</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41614</t>
+          <t>40769</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>62,43%</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34650</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51922</t>
+          <t>51974</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26374</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42428</t>
+          <t>41906</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65117</t>
+          <t>63787</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88065</t>
+          <t>87536</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59300</t>
+          <t>59314</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76718</t>
+          <t>76846</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>69287</t>
+          <t>69309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86851</t>
+          <t>87106</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>134822</t>
+          <t>134029</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>158713</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>245</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>748</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>10812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>747</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>773</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11814</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18037</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>30767</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>25607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43978</t>
+          <t>44482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>38125</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50532</t>
+          <t>50711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37526</t>
+          <t>35860</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52476</t>
+          <t>51920</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>79529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99524</t>
+          <t>99335</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,96%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13837</t>
+          <t>13777</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22630</t>
+          <t>22442</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>25051</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>30958</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45307</t>
+          <t>44532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18242</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>9430</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25653</t>
+          <t>25984</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19453</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36717</t>
+          <t>37093</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36407</t>
+          <t>36578</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57437</t>
+          <t>58511</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62380</t>
+          <t>61777</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>78649</t>
+          <t>78912</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65189</t>
+          <t>65552</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84973</t>
+          <t>84357</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131869</t>
+          <t>131681</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>156877</t>
+          <t>157602</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
